--- a/regulatory-compliance/cloud-foundation/9.1/nist-ai-100-1/vcf-91-companion-nist-ai-100-1.xlsx
+++ b/regulatory-compliance/cloud-foundation/9.1/nist-ai-100-1/vcf-91-companion-nist-ai-100-1.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="190" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Version 910-20260612-01</t>
+          <t>Version 910-20260623-01</t>
         </is>
       </c>
     </row>
@@ -536,17 +536,16 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Disclaimer</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Additional Resources</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
-This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+          <t>This is one of a library of companion guides that map VMware Cloud Foundation and its advanced services to security and compliance frameworks. For each framework, the guide is published as a spreadsheet, a CSV data file, a Markdown document, and a PDF, together with a Security Configuration Guide crosswalk that identifies the VCF technical hardening settings relevant to that framework. The companion guide library, the VMware Cloud Foundation Security Configuration Guide, and related security documentation, sample scripts, and Q&amp;A are available at https://brcm.tech/vcf-security.</t>
         </is>
       </c>
     </row>
@@ -554,12 +553,28 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
+This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Copyright (c) CA, Inc. All rights reserved.
 You are hereby granted a non-exclusive, worldwide, royalty-free license under CA, Inc.'s copyrights to use, copy, modify, and distribute this software in source code or binary form for use in connection with CA, Inc. products.
@@ -568,16 +583,16 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Third Party Identifiers and Mappings</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>This document includes regulatory compliance and security control identifiers from external sources as a convenience to end users. This does not constitute endorsement, in either direction.
 There is not a one-to-one mapping of product capabilities to third-party controls. A product capability, or set of capabilities, may be applicable to multiple controls. Conversely, a control may be satisfied with the use of multiple capabilities.
@@ -1159,18 +1174,9 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>VCF contributes to asset inventory processes by maintaining a detailed, real-time inventory of technology assets across compute, storage, and networking layers.
-VMware vCenter maintains the authoritative inventory of all managed objects in the environment. The vSphere inventory organizes objects in a hierarchical structure beginning at the root folder and extending through datacenters, clusters, hosts, virtual machines, networks, and datastores. Each object carries metadata including configuration details, resource allocations, and operational state. Administrators can extend this metadata by defining custom attributes, which store organization-specific fields against any inventory object in vCenter. Custom attribute values are held centrally by vCenter rather than within the individual objects, allowing teams to annotate VMs, hosts, datastores, and other inventory items with organization-defined information such as ownership, classification, or business justification details. This inventory reflects the live state of the environment as objects are created, modified, or removed. Multiple vCenter instances can be linked for centralized inventory management across workload domains.
-Programmatic access to the full inventory is available through the vSphere Web Services API. The Property Collector service uses Property Filter Specifications to identify inventory elements either directly or through object property traversal. The RetrievePropertiesEx method collects properties from inventory objects, allowing external systems and automation scripts to enumerate assets, gather configuration details, and build reports at whatever level of granularity is needed. The SimpleClient sample application demonstrates how to connect to a vCenter instance and obtain a listing of top-level inventory entities along with their properties and references.
-VCF Operations extends inventory visibility by retrieving inventory details from each vCenter, including associated clusters, VMware ESX hosts, datastores, and virtual machines. Discovered objects are grouped logically in detailed inventory lists, and the inventory management interface supports sorting, searching, and object tagging to organize assets at scale. Custom object groups are containers that collect data from included objects and report on the data collected, allowing administrators to create dashboards and widgets that display resource information for grouped assets. VCF Operations also applies policies to newly discovered objects, such as objects added to an object group. ResourceAttribute elements define the metrics that appear in the monitoring interface, each identified by a Metric Key, providing continuous visibility into asset utilization, capacity, and health. The vSphere Compute Inventory Dashboard provides interactive views of clusters, hosts, and virtual machines associated with any selected object.
-For application-level visibility, the VCF Operations Service Discovery adapter discovers running applications and services along with their CPU and memory metrics. Discovery rules can be defined using object types including metrics, relationships, properties, object names, and tag-based criteria. Discovered applications can be grouped by object type and selected attributes through Application Definition criteria, and the results can be exported in CSV format for use in external asset tracking systems.
-VCF Automation adds a consumption-oriented layer to asset tracking. Projects link users, catalog items, and infrastructure resources where deployments are provisioned. The Overview tab displays infrastructure and consumption metrics across the organization. Resources visible in inventory views are scoped by the rights and project roles assigned to each user, providing role-appropriate visibility for audit and review. When catalog items are deployed, they are provisioned against the infrastructure available to the selected project, creating a traceable relationship between the request, the deployment, and the underlying resources. Provider accounts can create and track assets including virtual machines, catalogs, templates, and media. Organizations in VCF Automation support policy-based governance on resource usage, allowing IT teams to monitor resource consumption, control permissions, and provide managed services with network isolation. Each organization maintains a secure boundary from other organizations. Resource quota policies can be defined through the Policies API to limit resources consumed by each user, project, or organization. Day 2 Action policies restrict which users have access to specific lifecycle operations on deployed resources. Tags within VCF Automation express capabilities and constraints that define deployments, and cloud administrators can place constraint tags on projects to exercise governance over resource provisioning, supporting asset classification and controlled placement of workloads across the infrastructure.
-For integration with external asset registries, VCF provides multiple paths. The Management Pack for ServiceNow in VCF Operations discovers and synchronizes asset details including CPU count, CPU speed, CPU type, disk space, RAM, serial number, manufacturer, model ID, OS version, IP address, and vCenter reference through the ServiceNow Table API and CMDB Meta API. These properties are marked as required discovery fields, keeping the external CMDB aligned with the actual virtual infrastructure. VCF Operations for Networks supports adding ServiceNow as a CMDB data source to fetch configuration items and their relationships. VCF Automation also integrates with ServiceNow for ITSM and CMDB synchronization, configurable through extensibility action scripts or through VCF Operations Orchestrator Client hosted workflows. The ServiceNow ITSM Plug-in for VCF Automation captures extensive asset metadata, including resource name, operational status, project assignment, storage details, account and region information, endpoint type, zone, environment, and custom properties. The plug-in stores machine resource records in custom ServiceNow CMDB tables that track creation timestamps, deployment IDs, machine IDs, entitled users, and network schema. Deployment records similarly capture blueprint version, project ID, catalog ID, organization ID, operational status, owner, requester, and expiration tracking. The plug-in supports day-2 resource lifecycle actions such as Add Disk, Resize, Power On/Off, Create Snapshot, and Delete, and maintains CMDB accuracy through reconciliation.
-Software asset tracking is supported through vSphere Lifecycle Manager, where software depots contain both the payloads and metadata for software updates. VCF Lifecycle Management tracks different versions of software components to help maintain compatibility across the infrastructure. The VCF Operations API includes methods to register associated products with their product name, version, and deployment details, contributing to a software-level view of the environment.
-The Consumption layer of VCF extends asset inventory to containerized workloads running on VMware Kubernetes Service (VKS) and vSphere Supervisor. The Kubernetes API server maintains a live registry of every object within a cluster or Supervisor namespace, covering pods, deployments, services, ConfigMaps, Secrets, PersistentVolumeClaims, CustomResourceDefinitions, and other resource types. Every resource carries standard metadata including name, namespace, labels, annotations, creation timestamp, and owning references that administrators can query or export at any level of granularity. Labels and annotations allow teams to attach arbitrary metadata to any Kubernetes resource, such as application name, business unit, or data classification, and these fields are queryable via label selectors, supporting filtered inventory exports by category. Supervisor namespaces map to vCenter namespaces, associating Kubernetes workloads with the organizational units defined during provisioning, and resource quotas and limit ranges attached to each namespace record the allocated capacity and support tracking of resource consumption by application or team.
-For workloads that consume specialized hardware such as accelerators or dedicated network devices, the Kubernetes Device Plugin framework provides hardware-level asset visibility within VKS clusters. Administrators or device owners use DeviceClasses to define sets of devices available in the cluster, and workloads claim specific hardware resources by creating ResourceClaims that filter for device parameters declared in a DeviceClass. Monitoring agents for device plugin resources discover which devices are in use on each node and collect metadata that associates each device allocation with the specific container consuming it, extending hardware asset tracking to the workload level.
-The Harbor Registry Supervisor Service provides an inventory mechanism for container images and artifacts. Harbor organizes images in a Projects structure by team or application and secures them with policies and role-based access control, allowing administrators to track which container images are authorized for use within the environment. Container images deployed through VCF consumption paths should be scanned, signed, and approved according to organizational software supply chain policies before use; digital certificates and validation mechanisms support supply chain assurance of images and artifacts. Where GitOps practices are in use, the Argo CD Supervisor Service extends this inventory capability by recording application synchronization events with timestamps, capturing the resource group, kind, namespace, name, sync status, and health status of each synchronized resource. Git repositories serve as the single source of truth for desired application and infrastructure state in a GitOps workflow, and infrastructure as code stored in version control creates a durable audit log of every authorized change to that state.
-These capabilities give VCF a strong technical foundation for tracking virtual infrastructure assets with accurate, real-time data at multiple levels of granularity. However, the broader requirements of this control, including business justification tracking, organization-defined accountability information, and formal review and audit processes for the full scope of technology assets, applications, services, and data, require organizational policies and processes that operate alongside the platform's inventory capabilities.</t>
+          <t>VMware Private AI Services (PAIS) provides a centralized inventory of AI models through the Model Gallery in Harbor Registry. Each model gallery has a unique name and is organized within Harbor projects with configured user access controls. Model revisions are stored as OCI artifacts with immutable manifests, and each revision is assigned a unique digest, giving a verifiable record of every model version in the inventory.
+OCI metadata describes model contents and dependencies, supporting identification of compatible platforms and giving visibility into what each model requires. The vcf pais models list command retrieves and displays all models available in a model gallery, giving operators a direct inventory view. Model Runtime tracks which models are actively deployed to inference endpoints, distinguishing between stored and deployed models.
+For third-party AI components, PAIS validates running AI workloads based on NVIDIA GPU Cloud (NGC) containers, a curated catalog of GPU-optimized, pre-tested containers. In disconnected environments, a Harbor registry stores container images from the NGC catalog, acting as a controlled intermediary that makes third-party AI components visible and trackable within the organization's infrastructure.</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -1245,24 +1251,17 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>VCF provides several capabilities that support secure logical disposal and sanitization of virtual resources, though the physical destruction or secure disposal of hardware remains an organizational responsibility outside VCF's scope.
-vSAN data-at-rest encryption uses a two-tier key architecture with Key Encryption Keys (KEK) and Data Encryption Keys (DEK), managed through an external Key Management Server (KMS) or vSphere Native Key Provider. When decommissioning encrypted storage, destroying the encryption keys renders the data unrecoverable without requiring a full disk wipe, a technique known as cryptographic erasure. vSAN also provides an "Erase disks before use" option during encryption configuration that wipes existing data from storage devices. For devices being added to or removed from vSAN disk groups, residual data and partition information can be cleaned before the device is reclaimed or released. Administrators can wipe ineligible disks through the vSAN Management API after verifying the partition table and stored data. vSphere provides API methods for cryptographic key lifecycle management, including removeKey and removeKeys operations that delete encryption keys from host caches. These methods support a force parameter for definitive key removal.
-VCF Operations includes a Reclamation dashboard and associated settings that help administrators identify virtual resources eligible for cleanup and disposal. The Reclamation Settings interface surfaces powered off VMs, idle VMs, snapshots, and orphaned disks, quantifying the resources that can be reclaimed. The Datastore Capacity Dashboard and ESX Capacity Dashboard both identify three specific reclamation opportunities: powered off VMs, snapshots, and orphaned VMDKs. These dashboards give operations and capacity teams visibility into resources that should be reviewed for secure removal before equipment is repurposed or decommissioned. The Reclamation Report tracks CPUs reclaimed, memory reclaimed, and storage reclaimed across different time periods, providing evidence of resource cleanup activity.
-For the actual deletion of virtual resources, VCF Operations provides a DELETE VM(s) capability that removes selected powered off VMs, and a RECLAIM RESOURCES function that allows immediate execution of resource reclamation processes. VCF Automation extends this with a Delete action on Deployments that destroys an entire deployment and deletes all associated resources for reclamation. VCF Automation also supports the creation and deletion of secret reusable properties through its secrets management interface under Administration Secrets, which is relevant when sanitizing credential material before equipment reuse.
-VCF Operations can disable virtual disk wiper and disk shrink operations on virtual machines through the isolation.tools.diskWiper.disable setting, which blocks data recovery attempts from within guest operating systems.
-Core dump handling is another area where VCF provides disposal-relevant guidance. VMware recommends considering disabling core dumps on VMware vCenter systems to protect sensitive information. Unlike virtual machine core dumps, which are encrypted when VM encryption is active, vCenter core dumps are not encrypted by default; vCenter systems support core dump encryption through the core-dump-encryption setting, and encrypted core dumps can be decrypted or re-encrypted as needed. Core dumps may contain sensitive information such as host keys, and organizations should follow their security and privacy policies to protect this data. When decommissioning or repurposing hosts, addressing core dumps is an important step for reducing the likelihood of information recovery.
-VCF also recommends securely deleting decrypted backup files after restore operations for VCF Operations, vCenter, and NSX components.
-Auditors should verify that the organization has defined procedures for securely disposing of or repurposing VCF-managed infrastructure. This includes confirming that virtual resources (VMs, snapshots, orphaned disks, secrets) are deleted through VCF's reclamation and deletion tools before physical equipment is removed from service, and that encryption keys are destroyed via cryptographic erasure for storage that held sensitive data. Physical chain-of-custody procedures, media sanitization verification, and equipment tracking through the disposal lifecycle are organizational processes outside the scope of VCF.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -2486,54 +2485,37 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>VCF provides a broad set of infrastructure-level capabilities that support business continuity and disaster recovery planning. While VCF does not itself constitute a Business Continuity Management System, it supplies the technical mechanisms that underpin resilient deployments and contingency operations.
-vSAN stretched clusters allow organizations to extend a single vSAN datastore across two geographically separated sites with an independent witness host. When configured with site mirroring, a stretched cluster can tolerate the complete loss of one site while maintaining data availability. vSphere HA, when enabled on a stretched cluster, automatically restarts virtual machines on the surviving site during a site failure. To support this, vSphere HA admission control should be configured to reserve 50% of the cluster's aggregate CPU and memory resources for failover, and site-specific isolation response addresses should be defined so that vSphere HA can validate host isolation even when network connectivity between sites is lost. The admission control setting for host failures the cluster tolerates should also be updated after cluster expansion to reflect the correct host count per availability zone. When stretching a workload domain cluster, the default management vSphere cluster must already be stretched. vSphere HA uses network heartbeats to validate the state of VMware ESX hosts, and can also use heartbeat datastores mounted to more than one host (excluding vSAN datastores) for cluster membership monitoring.
-vSphere HA also operates at the individual cluster level independent of stretched clusters. The HA configuration remediation mode can be set to quarantine mode, maintenance mode, or mixed mode to handle host failures in a controlled manner, helping maintain workload availability during hardware events. vSphere Fault Tolerance provides a higher tier of availability for individual virtual machines by maintaining a secondary VM in continuous lockstep with the primary, enabling instantaneous failover with no data loss if the primary host fails.
-vSAN Data Protection provides snapshot-based protection through the vSAN Snapshot Service. Protection groups support configurable snapshot scheduling with adjustable intervals and retention policies that define retention duration and time units. This allows organizations to define data protection policies aligned with their recovery point objectives. The Snapshot Service API also supports operations such as restoring deleted virtual machines from snapshots and creating linked clones from snapshots.
-vSphere Replication provides asynchronous replication of virtual machines with a configurable Recovery Point Objective (RPO), allowing organizations to replicate workloads to a secondary site and define acceptable data loss windows as part of their contingency planning.
-VCF requires all management components, including VCF Operations, VMware vCenter, NSX, and VCF Automation, to be configured with a regular backup schedule and retention policy. VCF Operations configures NSX Manager backups during the initial deployment, with a recommended backup frequency of hourly and 7-day retention. Backup jobs for VCF Operations and all vCenter instances should start within the same 5-minute window to capture a consistent state. The VMware Infrastructure Health adapter within VCF Operations monitors backup job retention for management components, including NSX Manager. Changed Block Tracking (CBT) tracks modified disk sectors on virtual machines to support incremental backups, reducing backup windows and storage requirements for VM-level backup operations. vCenter itself also supports a High Availability configuration with Active and Passive nodes whose configuration files are continuously replicated, providing management-plane resilience independent of the backup schedule.
-VMware HCX provides workload mobility capabilities for migrating and replicating VMs between sites. HCX supports multiple migration types through its Mobility Agent service, including vMotion, Cold Migration, Bulk Migration, and Replication Assisted vMotion (RAV), each addressing different scenarios from large-scale parallel migrations to zero-downtime live migrations. HCX also includes appliance-level backup and restore capabilities for the HCX Manager, including certificate backup and restore, supporting planned migrations and recovery scenarios as part of broader BC/DR operations.
-VCF Operations monitors infrastructure health and surfaces alerts when conditions threaten availability, giving operations teams early warning of potential failures. The Platform Health Alerts page provides a centralized view of alerts across data sources and infrastructure nodes. VCF Automation provides alerts through the associated VCF Operations application for capacity, performance, and availability monitoring. VCF Operations also includes infrastructure planning and what-if analysis capabilities that help organizations forecast capacity requirements and plan for contingency scenarios. Committed scenarios reserve capacity by setting aside resources for new, upcoming, or planned workloads, helping stakeholders understand capacity requirements across the environment. Integration with IT Service Management and Configuration Management Database platforms is supported through VCF Automation, enabling organizations to tie their infrastructure management into broader service continuity workflows.
-Lifecycle management tools allow administrators to plan updates and schedule maintenance windows to make changes with minimal disruption to services, supporting the operational continuity aspect of business continuity planning.
-While VCF provides these technical capabilities, a complete BCMS requires organizational elements that fall outside the platform: documented continuity of operations plans, recovery time and recovery point objectives defined by business stakeholders, regular testing and exercise of recovery procedures, communication plans, and management oversight of the continuity program. VCF supplies the infrastructure resilience and recovery mechanisms that such plans depend on, but the planning, governance, and procedural components must be established and maintained by the organization.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to business continuity by providing security-layer continuity mechanisms that remain active during disaster recovery events and workload migrations. NSX Federation Security maintains security posture across data centers during disaster recovery and workload migration, preserving distributed firewall and gateway firewall policies so that enforcement continues through failover.
-The Security Services Platform, which provides the underlying infrastructure for vDefend's threat detection and inspection services, supports vSphere High Availability configurations. When a VMware ESX host becomes unhealthy, vSphere HA migrates the affected Security Services Platform virtual machines to healthy hosts in the cluster, restoring threat detection capacity without manual intervention. VMware recommends enabling vSphere HA for host-level failure recovery and configuring a storage policy with RAID for datastore-level failure tolerance in Security Services Platform deployments.
-Security Services Platform can also be deployed on a vSAN stretched cluster configuration, which replicates storage across two physically distinct sites connected by a high-bandwidth or low-latency inter-site link. This configuration requires a minimum of two sites with their own hosts and a witness host to handle potential conflicts arising from network partitions, supporting site-level failure scenarios.
-When vSphere HA restarts workload VMs on a new recovery host after a failover, the vDefend distributed firewall automatically reinspects all traffic from those VMs on the receiving host, because the Flow Table contents cannot be moved between hosts during host recovery. Security policy enforcement resumes on the new host without manual reconfiguration.
-The broader BCMS framework, including Continuity of Operations Plan and BC/DR playbooks, impact analyses, and organizational governance processes, is outside vDefend's scope and must be established through dedicated business continuity management programs.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides the technical execution layer for contingency planning in virtualized infrastructure. Recovery plans define the sequence, priority, and configuration for failover operations, acting as executable BC/DR playbooks. Protection groups organize virtual machines into logical units aligned with application tiers or business functions, establishing the scope of each contingency plan.
-Recovery plans support non-disruptive testing before use in planned migration or disaster recovery, allowing organizations to validate their contingency procedures without affecting production workloads. Recovery plan configuration differs between emergency scenarios at the protected site and planned migration of services from one site to another, with PNR supporting both modes. A forced recovery function is available during disaster recovery plan execution for scenarios requiring immediate failover.
-vSphere Replication provides host-based replication with configurable Recovery Point Objectives (RPO), allowing organizations to set per-workload data loss tolerances. vSphere Replication supports up to 200 point-in-time recovery instances per virtual machine using the Latest Instances option, enabling recovery to specific earlier states. This capability is relevant to contingency scenarios involving data corruption or ransomware events. When the source site is accessible at the time of recovery, vSphere Replication can synchronize recent changes from the source site to the target site before completing the operation, reducing data loss.
-In 9.1, PNR extends to multi-tenant disaster recovery through integration with VCF Automation. The product implements role-based access control with Organization Administrator, Project Administrator, and Project Advanced User roles, each with defined authorization levels for disaster recovery operations. Role assignments must be configured on both the primary and secondary PNR sites to maintain consistent access control across the DR environment. A multi-region deployment topology places separate management domains in each region to contain disaster impact to one region, while enabling service recovery in an alternate management domain when VCF Automation and VCF Operations are affected. The VCF Operations Orchestrator Plug-In for PNR provides Configuration, Inventory Mappings, Protection Groups, and Storage predefined workflow categories for workflow-driven recovery operations.
-Cyber recovery deployments support a standard VCF topology where the workload domain is isolated from the management domain, providing separation between management and user workloads in clean-room recovery scenarios.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K26" s="10" t="inlineStr">
@@ -2548,19 +2530,12 @@
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides application-layer resilience mechanisms at both the control plane and the data plane that organizations can incorporate into business continuity plans for application delivery services.
-At the control plane, the Avi Controller is deployed as a cluster with continuous configuration replication across all nodes, providing management-plane redundancy so that a single Controller node failure does not interrupt application delivery operations. Avi supports deployment of the Controller cluster across two availability zones, with vSphere HA recommended to support recovery of any node that fails in the secondary zone. For single-node deployments, enabling vSphere HA on the Controller VM is recommended for node recovery following a host failure. The Avi Controller provides configuration backup and restore capability that supports disaster recovery and configuration migration across Controller instances; organizations should capture and retain Controller backups as part of their continuity documentation.
-Availability Zone awareness in Avi allows multiple availability zones to be configured, each defining a subset of vCenter instances, hosts, and datastores that share a fault domain. Configuring availability zones during Service Engine Group setup distributes data-plane capacity across isolated failure domains, supporting continuity designs where application delivery capacity remains available if one fault domain becomes unavailable.
-At the data plane, Avi's Elastic High Availability mode provides fast recovery for individual virtual services following Service Engine failure. In vSphere DRS-enabled clusters, virtual service recovery occurs before vSphere HA brings up a replacement Service Engine when virtual service slots are available in other Service Engines, giving the application delivery layer its own recovery path distinct from the infrastructure restart cycle. If vSphere HA does not recover the failed Service Engine within a configured timeout period, the Avi Controller resumes recovery independently. Service Engine VMs should be deployed on vSphere clusters configured with both HA and DRS in fully automated mode; when Avi is deployed with VMware Kubernetes Service (VKS) on VCF, DRS and HA are required on every vSphere cluster used with Avi.
-For Kubernetes environments, the Avi Multi-Cluster Kubernetes Operator (AMKO) provides federation architecture that supports disaster recovery across Kubernetes clusters. AMKO designates a leader cluster and multiple member clusters, coordinating application delivery failover as part of a multi-cluster DR strategy.
-Avi ControlScripts, used in conjunction with the alert framework, can perform automated failover actions such as adding or removing routes based on VIP attachment and detachment events, allowing organizations to define automated remediation workflows that respond to system events without manual administrator intervention.
-In 9.1 deployments using VCF Automation, Avi's Central Licensing maintains a global capacity pool that removes the requirement for duplicate licenses in DR scenarios, supporting license continuity across failover sites.
-Organizations should document these mechanisms, including the Elastic HA configuration, Controller cluster topology and backup schedule, availability zone placement, and AMKO federation design, in their Business Continuity and Disaster Recovery playbooks. The technical recovery capabilities are built into the product; the planning artifacts, testing procedures, and escalation workflows are organizational responsibilities that extend beyond what Avi provides.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -2669,10 +2644,11 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) provides a workflow for evaluating AI TEVV results before a model reaches production deployment. MLOps engineers validate ML models onboarded to PAIS against the organization's security, privacy, and technical requirements, which establishes a checkpoint that TEVV results inform.
-Deep Learning VMs and the Model Endpoints feature give MLOps engineers the testing environment where TEVV activities produce results to be evaluated. Completion and embedding models run on GPU through the open-source vLLM inference engine, and A/B testing of embedding models is recommended so teams can compare model performance in real-world settings before promotion.
-Performance and behavioral telemetry to interpret TEVV results comes from PAIS observability. vGPU metrics are collected by the DCGM Exporter and visualized in Prometheus and Grafana for performance analysis, and MLOps engineers and application developers monitor model health, quality, and behavior in agent applications through observability platforms such as Grafana. PAIS controller pod metrics are streamed to VCF Operations through the Telegraf agent running on the Supervisor instance, and GPU metrics can be reviewed at cluster, host system, and host properties levels in VCF Operations. Observability is enabled as part of PAIS activation in VCF Automation and is configured by uncommenting the spec.observability.prometheusRuntime section of the PAISConfiguration CR.
-PAIS provides the workflow checkpoint, the testing surface, and the monitoring tooling. The interpretation of TEVV results and the viability determination remain organizational decisions made by MLOps engineers and AI leadership.</t>
+          <t>VMware Private AI Services (PAIS) provides technical mechanisms that help organizations evaluate AI model viability before production deployment. Deep learning VMs provisioned from PAIS images support pre-deployment prototyping, fine-tuning, validation, and inference workloads on the same GPU-accelerated infrastructure used in production, so viability assessments are performed against representative conditions. Data scientists can download models from public or organizational container registries and use DL VMs to assess whether they achieve intended objectives before investing in production deployment.
+PAIS uses a private OCI-compliant registry, typically Harbor, as a gate between validation and deployment. A Harbor administrator must create a project for PAIS in the private Harbor registry before deployment, and OCI-compliant registries from other vendors are also supported. MLOps engineers validate models against the security, privacy, and technical requirements of the organization before publishing to the registry, and only models that pass this gate become available for catalog-driven provisioning.
+PAIS catalog items in VCF Automation are the mechanism by which validated models reach end users. An administrator adds catalog items for provisioning AI applications, then verifies that PAIS catalog items are available to members of the selected project and monitors the provisioning process before broad release. PAIS deployment leases can be created to control how long a deployment can exist, which supports time-bounded pilot or evaluation deployments that conclude with a documented go or no-go decision.
+PAIS supports ongoing viability evaluation through observability integration. MLOps engineers and application developers can monitor models used in agents through observability platforms such as Grafana and VCF Operations to track the health, quality, and behavior of AI applications. Metrics collection is activated through the spec.observability.prometheusRuntime section of the PAISConfiguration custom resource, with a configurable storage class and metrics retention period. PAIS knowledge base operations record timing metrics for download, embedding generation, and indexing, giving the organization visibility into retrieval-augmented generation pipeline performance. When integrating external capabilities through the Model Context Protocol, PAIS requires examination and approval of MCP server tools and capabilities before they can be used in agents, so the organization can confirm suitability against its standards.
+The criteria themselves, the decision authority, and the broader development and deployment governance workflow remain organizational responsibilities outside the platform.</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -3292,12 +3268,12 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (VMware vDefend and Advanced Threat Protection) contributes to multiple phases of the incident handling lifecycle through network-layer detection, multi-signal analysis, and automated containment capabilities.
-For detection and event intake, Security Intelligence categorizes detected suspicious traffic events by impact type, assigning Critical, High, Medium, or Low severity to help teams prioritize response. Security Intelligence also maps detections to MITRE ATT&amp;CK tactics and techniques and records occurrence counts over configurable time windows, providing the structured event context that analysis workflows require.
-For analysis, Malware Prevention generates File Analysis Reports and Process Analysis Reports that detail the types of activities detected during artifact inspection. File Analysis Reports classify detected behaviors across categories including Autostart, Disable, Evasion, File, Memory, Network, Reputation, Settings, Signature, Steal, Stealth, and Silenced, and include an ATT&amp;CK TECHNIQUES field that records observed malicious actions or tools. Process Analysis Reports document in-memory script buffer inspection results and carry an Analyst UUID to track individual inspection events. Malware Prevention Service event logs capture file type, file size, inspection timestamp, client VM ID, submission source, detection status, verdict, and analysis status for each inspected file. The Malware Prevention Dashboard aggregates file and process event details and inspection results for operator review. Network Detection and Response (NDR) Campaign Correlation Rules correlate labeled file and process detections, including AV labels and PCAP matches, with matching IDS events on the same compute, supporting multi-signal analysis during investigation. The Security Services Platform assigns a Security Operator role dedicated to monitoring security systems and responding to security incidents.
-For containment and eradication, Intelligent Assist supports remediation by allowing selection of a Targeted Strategy for surgical, focused containment or a Comprehensive Strategy for broader remediation across potentially affected workloads. The Security Segmentation Report's Overview section summarizes inter-environment policies and rules, providing traffic flow context that can inform containment scope. Security Explorer's ratio of detected versus prevented events helps operators assess how effectively controls are operating during active response.
-A limitation applies to automated remediation: objects generated during Intelligent Assist or NDR remediation that encounter errors require manual cleanup, so recovery activities may require human intervention beyond automated policy actions. vDefend IDS/IPS also applies a severity-based prioritization under memory pressure, dropping lower-severity events (Low and Informational) first before Medium, High, and Critical, which operators should account for when assessing detection completeness during an investigation.
-Preparation and full organizational recovery rely on processes and tooling outside vDefend's scope.</t>
+          <t>VMware vDefend contributes to incident response operations by providing integrated threat detection, investigation, correlation, and remediation capabilities within the network security layer of VCF. Security Services Platform defines a Security Operator role specifically for monitoring security systems and responding to security incidents, providing a built-in responsibility model for incident response activities at the network security layer.
+Security teams can investigate individual threat events and correlated campaigns through the Security Services Platform interface to assess impact, identify root causes, and take appropriate mitigation actions. The Campaign Blueprint feature visualizes correlated security events and key actors within a campaign, simplifying triage and investigation to reduce mean time to detection. Campaign correlation surfaces multi-stage attack patterns: a drive-by infection event followed by a command-and-control event on the same workload is linked into a single campaign view. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions.
+Network Detection and Response (NDR) provides security analysts with capabilities to understand security events, triage them, and remediate by creating policies. NDR includes Suspicious Traffic detectors that collect and display suspicious traffic detections as events. Each detection event receives an impact score calculated from Confidence and Severity; informational events with scores from 1 to 24 indicate activity that is not essentially malicious and help teams focus attention on higher-priority events.
+Security Services Platform generates Security Segmentation Reports and Blast Radius Reports that break down at-risk workloads, communication chains, and flows, helping teams assess the potential scope and lateral spread of an incident. The Rule Analysis feature generates downloadable CSV reports of anomaly analysis results, with separate files for each detected anomaly type. Security Services Platform provides metrics for Malware Prevention Service events, including malware family, non-benign indicators, process inspection events, and process state data, accessible through the API.
+For remediation, the Response and Remediation feature in Security Services Platform performs automated policy creation based on user role and permissions. Intelligent Assist supports two remediation strategies, Targeted (surgical, with potentially lower breadth) and Comprehensive (broader scope), allowing teams to select the appropriate approach for each incident. Security Services Platform collects IDS policies, rules, and security profiles created by Intelligent Assist as part of remediation operations. Objects generated during NDR remediation that encounter errors require manual cleanup in Intelligent Assist.
+These capabilities support detection, investigation, and remediation phases of an incident response lifecycle at the network security layer. vDefend does not govern organization-wide incident response processes, maintain incident response documentation, or manage incident tracking and status coordination functions. Those organizational and process governance functions fall outside the scope of a network security product.</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -6196,6 +6172,166 @@
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
+          <t>VCF contributes to monitoring deployed AI workloads through VCF Operations, which provides continuous visibility into the health, performance, and capacity of the infrastructure those workloads run on. VCF Operations dashboards display real-time and historical metrics for compute, storage, and networking resources consumed by AI VMs. VCF Log Management aggregates log data across the stack. VMware vCenter alarms trigger on configurable thresholds for CPU, memory, disk, and network conditions.
+For AI and autonomous technology workloads deployed as containerized applications on VMware Kubernetes Service (VKS) clusters, the platform provides a layered observability stack. The Prometheus Standard Package, available for deployment on VKS clusters, collects metrics from configured targets at defined intervals, evaluates alerting rules, and forwards alerts to Alertmanager. The package includes prometheus-server, which handles scraping, rule processing, and alerting, as well as prometheus-kube-state-metrics for tracking node status, replica-set compliance, pod and job status, and resource requests and limits across namespaces. For batch inference or training jobs that cannot be scraped directly, Prometheus Pushgateway accepts pushed metrics. Grafana Operator pairs with Prometheus to provide dashboards and configurable alert thresholds, enabling operators to define visual representations of AI workload metrics and receive notifications when behavior deviates from expected patterns.
+Monitoring agents for Kubernetes device plugin resources, including GPUs commonly consumed by AI inference and training workloads, can be deployed as DaemonSets on worker nodes to track resource utilization and associate metrics with specific containers. The Kubernetes Node Problem Detector can be extended with custom monitoring scripts written in any language, which allows AI-specific health checks to be added without modifying core Kubernetes components. Kubernetes also provides built-in auditing capabilities for monitoring and recording cluster activities.
+Istio, available as a Standard Package for VKS clusters, provides mechanisms to secure, connect, and monitor services. For AI inference services that expose APIs, Istio supplies request rate, latency, and error rate metrics without requiring application-level instrumentation.
+Deployments using the Harness CI/CD Supervisor Service can integrate Dynatrace, which automatically instruments applications and infrastructure upon deployment and collects metrics, logs, and traces. The Dynatrace AI engine detects anomalies, identifies root causes, and generates intelligent alerts. The Dynatrace operator automates the deployment, scaling, and maintenance of the monitoring stack within the VKS cluster. Harness Service Reliability Management monitors deployed services post-deployment to calculate a real-time health score based on transaction success and latency.
+VKS cluster management proactively monitors the VKS cluster estate to confirm assigned policies are enforced correctly, and generates Policy Insights when configuration conflicts or environmental errors are detected.
+Monitoring AI model behavior at the application level, including model drift, inference accuracy, and data distribution shifts, requires organization-defined monitoring logic implemented using these platform tools. VCF and its Kubernetes consumption layer provide the collection, storage, and alerting infrastructure, but the organization must configure the signals to collect, define thresholds for AI-specific behavioral anomalies, and establish processes for reviewing and responding to monitoring data.
+VMware Private AI Services (PAIS) provides production monitoring for deployed AI workloads through metrics collection, telemetry, and integration with observability platforms. The Private AI Services controller exposes a Prometheus metrics endpoint on the pais-controller-manager service, and Private AI Services deployments include a Prometheus server pod that collects metrics for observability platforms. DevOps engineers visualize health and performance metrics for Private AI Services components running in a VCF Automation namespace using observability platforms such as Grafana.
+Observability is activated by updating the PAISConfiguration custom resource with parameters that enable metrics collection for observability platforms and LLM traces for the OpenTelemetry (OTel) Collector. When LLM traces collection is activated, MLOps engineers can analyze traces from agents and knowledge base indexing in the OpenTelemetry Collector, supporting observation of model behavior and application health in agentic workflows. Private AI Services supports sending traces to an OpenTelemetry collector over HTTP/protobuf or gRPC.
+Operators can monitor Private AI Services deployments in Grafana for pod restart frequency, vGPU licensing status, and idle or underutilized GPU devices in passthrough mode. Private AI Services controller pod metrics are integrated into observability platforms through Telegraf configuration in the Supervisor instance, which allows VCF Operations to ingest PAIS controller metrics alongside the broader infrastructure telemetry it already collects for GPU-enabled workload domains. Deployment health is verified through Kubernetes pod state of the API, ingress, rex worker, and Prometheus server pods.
+MLOps engineers and application developers can perform monitoring and diagnostics of models used in agents through observability platforms like Grafana to track the health, quality, and behavior of AI applications.</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>VMware vDefend contributes to monitoring the functionality and behavior of deployed AI workloads running on VCF by providing continuous network-level behavioral monitoring, threat detection, and AI-assisted security analysis around those workloads.
+Security Intelligence, running on the Security Services Platform, provides continuous network-level behavioral monitoring that detects new traffic flows, unauthorized communications, and anomalous activity around deployed systems, including AI workloads. It continuously monitors for new flows between environments and alerts administrators to unauthorized or unexpected traffic, supporting ongoing policy adjustments. The Segmentation Monitoring Dashboard provides dedicated views for monitoring environment-level traffic flows; when monitoring identifies an environment pair without a configured protection policy, it offers a Run Recommendations option to generate policy recommendations based on observed traffic. Security Intelligence provides Infrastructure, Environment, and Application Monitoring capabilities. The application monitoring view within the Segmentation Monitoring Dashboard surfaces metrics including unprotected flows and applications with unprotected rule hits, providing targeted visibility into workloads, including AI systems, that lack active firewall policy coverage. The Policy Recommendations monitoring capability checks for changes in monitored entity scope every hour when enabled. Security Intelligence also runs a scheduled daily classification job, automatically categorizing compute entities based on traffic flows observed over the prior 30 days.
+Intelligent Assist is an AI-assisted analysis feature accessible through the NSX Manager UI and Security Services Platform UI. It provides contextual analysis support on the IDS/IPS, Detections, and Campaigns pages, enabling administrators to investigate security events affecting deployed workloads with AI-driven guidance.
+IDS/IPS provides ongoing threat detection through monitoring dashboards scoped to both distributed and gateway deployments. Project-scoped dashboards display events triggered for specific projects, allowing targeted monitoring of AI workload deployments. Network Detection and Response (NDR) applies behavioral analysis to identify suspicious activity targeting monitored workloads. The NDR Sensor periodically checks the status of activated features on the Security Services Platform every 15 minutes and updates its configuration accordingly.
+Monitoring AI system functionality at the application layer, including model performance, output quality, and behavioral drift, is outside vDefend's domain and requires additional tooling.</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J75" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M75" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N75" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>MEASURE 2.5</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>AAT-01.2, AAT-10.9</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>The AI system to be deployed is demonstrated to be valid and reliable. Limitations of the generalizability beyond the conditions under which the technology was developed are documented.</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>VMware Private AI Services (PAIS) provides a model validation workflow with dedicated tooling and environments. MLOps engineers validate ML models onboarded to PAIS against the security, privacy, and technical requirements of the organization before publishing them to the model gallery. Validation is performed using deep learning VMs (DL VMs) provisioned from PAIS images, which support AI prototyping, fine-tuning, validation, and inference workloads on the same GPU-accelerated infrastructure used in production. The recommended practice is to distribute models that were validated on a DL VM rather than models pulled directly from the Internet, which could contain malicious code or be tuned for malicious behavior.
+After validation, models are stored in a central model gallery backed by a Harbor registry service running in the Supervisor cluster, or in an OCI-compliant container registry from another vendor. Storage in Harbor requires authentication and certificate-based trust for model retrieval. The model gallery acts as a publication gate: only models that have been validated and uploaded to the gallery are available for inference, either directly in PAIS Model Endpoints or on a DL VM running a Triton Inference Server from the NVIDIA NGC catalog. Models in the gallery are available for automated CI/CD-based deployment of model runtimes.
+After a model is in service, PAIS provides mechanisms for monitoring and evaluating model behavior. Model Endpoints expose a REST API for application integration and support A/B testing so MLOps engineers can compare the real-world performance of different embedding models. PAIS observability is activated through the PAISConfiguration custom resource to collect Prometheus metrics and OpenTelemetry traces, and model health, quality, and behavior can be monitored through observability platforms such as Grafana.</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J76" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L76" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M76" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N76" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>MEASURE 2.6</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>AAT-10.13, AAT-10.4, AAT-11.2</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>The AI system is evaluated regularly for safety risks – as identified in the MAP function. The AI system to be deployed is demonstrated to be safe, its residual negative risk does not exceed the risk tolerance, and it can fail safely, particularly if made to operate beyond its knowledge limits. Safety metrics reflect system reliability and robustness, real-time monitoring, and response times for AI system failures.</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
           <t>VCF contributes to post-deployment monitoring of AI workloads through VCF Operations, which provides continuous health, performance, and capacity monitoring for the infrastructure hosting those workloads. VCF Operations dashboards surface CPU, memory, storage, and network metrics for VMs running AI workloads. VCF Log Management aggregates and analyzes log data from VMware vCenter, VMware ESX, and NSX components. vCenter alarms provide threshold-based alerting for infrastructure conditions that could affect AI workload availability.
 For AI workloads running as containerized applications on VMware Kubernetes Service (VKS) clusters, the platform extends infrastructure-level observability to the Kubernetes layer. VKS clusters provisioned with the automated-monitoring label automatically receive monitoring configuration on each new node, integrating cluster telemetry with VCF Operations. The Prometheus standard package, installable on VKS clusters through the Supervisor Management Proxy Service, deploys kube-state-metrics, node-exporter, pushgateway, Prometheus, and Alertmanager as components. The prometheus-kube-state-metrics component monitors node status and capacity, ReplicaSet compliance, pod status, job and CronJob status, and resource requests and limits, providing continuous metric collection that can be directed at AI inference services or training job pods. Telegraf is available as a standard package that deploys as a Deployment component to scrape metrics from kube-state-metrics and node-exporter and forward them to external observability backends. Monitoring and alerting for Kubernetes deployments is also available through the Argo CD Supervisor Service using Grafana Operator and Prometheus.
 Kubernetes-native health probes and status tracking support workload condition detection at the pod level. Liveness and readiness probes can be configured on AI workload containers to detect unresponsive or overloaded model serving instances; a readiness probe removes the pod from service routing when it cannot handle requests, and a liveness probe triggers a container restart when the application becomes unresponsive. The Kubernetes Deployment controller continuously monitors running application instances and automatically replaces instances when nodes fail or are removed from service, providing a self-healing mechanism that addresses machine failure or maintenance. Kubernetes DeploymentStatus exposes observedGeneration and conditions fields with type, status, lastTransitionTime, and reason values, allowing operators to detect rollout failures, stuck deployments, or configuration drift from the expected specification. VKS cluster management proactively monitors the cluster estate to verify that assigned policies are enforced correctly, and generates Policy Insights when configuration conflicts or environmental errors are detected.
@@ -6207,169 +6343,6 @@
 Enabling these observability features, defining retention and alerting policy, and acting on monitoring signals are organizational process responsibilities. PAIS provides the monitoring infrastructure and integration points, but continuous post-deployment monitoring as a practice requires the organization to assign operational ownership, review observability data on an ongoing basis, and respond to anomalies in AI workload behavior.</t>
         </is>
       </c>
-      <c r="G75" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="H75" s="10" t="inlineStr">
-        <is>
-          <t>VMware vDefend (vDefend) contributes to proactive and continuous monitoring of deployed AI workloads running on VCF through multiple layers of ongoing network-level security monitoring.
-Security Intelligence continuously monitors for new flows between environments and alerts administrators to unauthorized or unexpected traffic, enabling ongoing policy adjustments as workloads evolve. It also monitors infrastructure services to detect newly deployed servers. A classification cron job runs automatically at 2:00 AM local time and repeats every 24 hours, evaluating traffic flows from the preceding 30 days to classify compute entities providing network infrastructure services. When the Recommendations Monitoring feature is enabled, Security Intelligence checks every hour for changes in the scope of monitored entities, allowing policy recommendations to remain current as AI workloads change. The Security Intelligence Flow Insights Dashboard supports detection and display of MITRE ATT&amp;CK framework tactics and techniques, showing counts of detected suspicious events per tactic and technique during a selected time period.
-Segmentation Monitoring provides dedicated views for environment-level traffic flows, accessible through the Monitor &amp; Plan interface. Administrators can monitor traffic between configured environment pairs, view flows related to detected infrastructure servers within specified time intervals, and export all unique flows to a CSV file for offline analysis or compliance evidence. The Environments monitoring window provides assessment of current security posture and enables improvement actions for environment pairs. When no protection policy is configured for an environment pair, Segmentation Monitoring offers a Run Recommendations option to generate policy recommendations, closing monitoring gaps around AI workloads.
-The Security Services Platform (SSP) collects metrics to monitor the readiness and performance of vDefend IDS/IPS in the environment. IDS/IPS engine statistics accessible per host include uptime, alert count, suppressed alerts, alert queue overflow status, engine ID, and last reload timestamp. IDS/IPS monitoring dashboards can be scoped to custom projects, displaying events triggered for that project only. For bare metal deployments, Bare Metal Agents stream metrics and detailed host-level telemetry to the SSP. The NDR Sensor periodically checks the status of activated features on the SSP every 15 minutes and updates its configuration accordingly.
-Intelligent Assist provides AI-assisted analysis within the NSX Manager UI and SSP UI, displaying on the IDS/IPS, Detections, and Campaigns pages to help administrators interpret monitoring data.
-Malware Prevention Service provides deployment status monitoring at the cluster level and per-node level, displaying deployment errors and individual transport node status. Network Detection and Response (NDR) applies behavioral analysis to detect suspicious activity targeting monitored workloads and correlates events into campaigns for investigation.
-Monitoring AI system functionality at the application layer, including model performance, output quality, and behavioral drift, is outside vDefend's domain.</t>
-        </is>
-      </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J75" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K75" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L75" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M75" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N75" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>MEASURE 2.5</t>
-        </is>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t>AAT-01.2, AAT-10.9</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>The AI system to be deployed is demonstrated to be valid and reliable. Limitations of the generalizability beyond the conditions under which the technology was developed are documented.</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t>VMware Private AI Services (PAIS) contributes to several of the design characteristics this control addresses, including reliability, security, resilience, and data privacy, through infrastructure-level mechanisms that apply to AI workloads deployed on VMware Cloud Foundation (VCF).
-Security. PAIS uses VCF SSO for identity and supports role separation across VI administrator, organization administrator, project administrator, DevOps engineer, data scientist, and MLOps engineer functions, with each role scoped to specific namespaces and operations. The Model Gallery is implemented as a Harbor project, and access to model artifacts is restricted to authorized users. Trust bundles establish authenticated HTTPS connections between PAIS components, the identity provider, the registry, and content management systems. GPU resource entitlements are scoped to the GPU-accelerated workload domain so capacity is not shared across domain boundaries.
-Reliability and resilience. PAIS workloads run on VCF, which provides vSphere High Availability for automatic VM restart on host failure, the Distributed Resource Scheduler for workload balancing, and vMotion for live migration of GPU-accelerated VMs when the supporting setting is configured. Cluster sizing guidance recommends maintaining unreserved GPU capacity and a dedicated failover host to accommodate planned upgrades and unplanned host failures. The Model Gallery stores ML models as OCI artifacts with immutable manifests and unique content digests, which supports rollback to a known-good model revision if a newly deployed model behaves incorrectly.
-Data privacy. PAIS isolates AI workloads in dedicated workload domains that can be deployed separately from the broader VCF environment. Namespace-scoped permissions restrict which users can access specific workloads and data. The Harbor registry replica architecture keeps the GPU-enabled workload domain isolated by proxying container images through a separate Internet-connected registry in a DMZ, with only registry push and pull traffic permitted between the two.
-Model integrity and validation. The validate-then-publish workflow requires MLOps engineers to validate ML models against the organization's security, privacy, and technical requirements before uploading them to the Model Gallery. PAIS scans models for serialization attacks before upload, and model integrity is verified through hash comparison of model files. Each revision pushed to the gallery receives a unique digest. Models can be validated for inference functionality and evaluated for performance and safety against business use cases before production deployment.
-PAIS does not address the fairness, transparency, or explainability characteristics this control names, because those properties belong to the AI models themselves rather than the infrastructure platform. Organizations must implement separate controls for bias testing, model interpretability, and output explainability at the application layer.</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I76" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J76" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K76" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L76" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M76" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N76" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>MEASURE 2.6</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>AAT-10.13, AAT-10.4, AAT-11.2</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>The AI system is evaluated regularly for safety risks – as identified in the MAP function. The AI system to be deployed is demonstrated to be safe, its residual negative risk does not exceed the risk tolerance, and it can fail safely, particularly if made to operate beyond its knowledge limits. Safety metrics reflect system reliability and robustness, real-time monitoring, and response times for AI system failures.</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E77" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t>VCF contributes to post-deployment monitoring of AI workloads through VCF Operations, which provides continuous health, performance, and capacity monitoring for the infrastructure hosting those workloads. VCF Operations dashboards surface CPU, memory, storage, and network metrics for VMs running AI workloads. VCF Log Management aggregates and analyzes log data from VMware vCenter, VMware ESX, and NSX components. vCenter alarms provide threshold-based alerting for infrastructure conditions that could affect AI workload availability.
-For AI workloads running as containerized applications on VMware Kubernetes Service (VKS) clusters, the platform extends infrastructure-level observability to the Kubernetes layer. VKS clusters provisioned with the automated-monitoring label automatically receive monitoring configuration on each new node, integrating cluster telemetry with VCF Operations. The Prometheus standard package, installable on VKS clusters through the Supervisor Management Proxy Service, deploys kube-state-metrics, node-exporter, pushgateway, Prometheus, and Alertmanager as components. The prometheus-kube-state-metrics component monitors node status and capacity, ReplicaSet compliance, pod status, job and CronJob status, and resource requests and limits, providing continuous metric collection that can be directed at AI inference services or training job pods. Telegraf is available as a standard package that deploys as a Deployment component to scrape metrics from kube-state-metrics and node-exporter and forward them to external observability backends. Monitoring and alerting for Kubernetes deployments is also available through the Argo CD Supervisor Service using Grafana Operator and Prometheus.
-Kubernetes-native health probes and status tracking support workload condition detection at the pod level. Liveness and readiness probes can be configured on AI workload containers to detect unresponsive or overloaded model serving instances; a readiness probe removes the pod from service routing when it cannot handle requests, and a liveness probe triggers a container restart when the application becomes unresponsive. The Kubernetes Deployment controller continuously monitors running application instances and automatically replaces instances when nodes fail or are removed from service, providing a self-healing mechanism that addresses machine failure or maintenance. Kubernetes DeploymentStatus exposes observedGeneration and conditions fields with type, status, lastTransitionTime, and reason values, allowing operators to detect rollout failures, stuck deployments, or configuration drift from the expected specification. VKS cluster management proactively monitors the cluster estate to verify that assigned policies are enforced correctly, and generates Policy Insights when configuration conflicts or environmental errors are detected.
-For organizations using Harness CI/CD on VKS, Dynatrace integration provides full-stack observability including application performance monitoring, infrastructure monitoring, and digital experience monitoring. The Dynatrace operator automates deployment, scaling, and maintenance of the monitoring stack within VKS clusters, and automatically correlates application deployment service metrics with underlying VKS infrastructure including nodes, pods, and the network. The Dynatrace AI engine detects anomalies, identifies root causes, and provides intelligent alerts. Harness SRM monitors deployed services post-deployment to calculate a real-time health score based on transaction success and latency.
-The VCF Automation Monitor tab provides deployment health information drawn from VCF Operations, and deployment cards in the self-service catalog surface deployment state, last request status, and operational history for workload deployments. AI-specific behavior monitoring (model accuracy drift, output quality) requires application-level tooling outside VCF's scope.
-VMware Private AI Services (PAIS) provides AI-specific monitoring mechanisms that support continuous post-deployment observation of AI workloads on VCF.
-At the PAIS layer, observability is activated by updating the PAISConfiguration custom resource with parameters that enable metrics collection and forward large language model traces to an OpenTelemetry Collector. PAIS deploys a Prometheus server pod for metrics collection that must be ready and running for observability to function, configured with a chosen storage class and a configurable metrics retention period. PAIS controller pod metrics are integrated into observability platforms through Telegraf configuration in the Supervisor instance, and the telegraf-user-config ConfigMap in the vmware-system-monitoring namespace manages user-configured monitoring endpoints for PAIS. The PAIS Supervisor Service exposes service-level metrics through pais.vmware.com that VI administrators access to monitor the health of the service.
-DevOps engineers visualize PAIS health and performance metrics in observability platforms such as Grafana, where dashboards report pod restart frequency, vGPU licensing status, and idle or underutilized GPU devices in passthrough mode. VI administrators visualize PAIS controller pod operation metrics in VCF Operations using the same metrics pipeline. MLOps engineers and application developers track the health, quality, and behavior of AI applications and the models used in agents through Grafana, supporting continuous observation of inference behavior. Model Endpoint deployment status can be verified using the kubectl get modelendpoints command, which returns the Ready status for each deployed endpoint, and the vcf cluster command-line interface provides cluster provisioning monitoring, registration, and kubeconfig retrieval for VKS clusters that host AI workloads. PAIS deployment leases can be configured to bound how long a deployment can exist, supporting lifecycle oversight of catalog-deployed AI workloads.
-Enabling these observability features, defining retention and alerting policy, and acting on monitoring signals are organizational process responsibilities. PAIS provides the monitoring infrastructure and integration points, but continuous post-deployment monitoring as a practice requires the organization to assign operational ownership, review observability data on an ongoing basis, and respond to anomalies in AI workload behavior.</t>
-        </is>
-      </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
           <t>Contributes</t>
